--- a/output_docs/doc3.xlsx
+++ b/output_docs/doc3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,9 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>11000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -460,7 +462,9 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2260</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -472,7 +476,9 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>6800</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -484,7 +490,9 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>1980</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -496,7 +504,9 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -508,7 +518,9 @@
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>90540.95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -520,7 +532,9 @@
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>14170.71</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -532,54 +546,50 @@
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>-3585.94</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BEDCHARGE: PRIVATE NON AC/Z B/711</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
+          <t>Pharmacy Bill</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>7000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMI PRIVATE NON AC</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>2000</v>
+        <v>12336.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BLOOD GASES</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>300</v>
+        <v>12336.72</v>
       </c>
     </row>
     <row r="13">
@@ -588,14 +598,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HAEMOGRAMIPANEL]</t>
+          <t>BED CHARGES BEDCHARGE: PRIVATE NON AC/Z B/711</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1260</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="14">
@@ -604,14 +614,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RFTIPANELI</t>
+          <t>BED CHARGES BEDCHARGE: SEMI PRIVATE NON AC/7 B/719 SEMIPrivate Non Ac</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="15">
@@ -620,14 +630,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
+          <t>PATHOLOGY INVESTIGATION :- BLOOD GASES</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
@@ -636,14 +646,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BSL ON GLUCOMETER</t>
+          <t>HAEMOGRAMIPANEL]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>130</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="17">
@@ -652,14 +662,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ECG CHARGES ER1</t>
+          <t>RFTIPANELI</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="18">
@@ -668,14 +678,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ER CHARGES rPD</t>
+          <t>DOCTOR FEES :- ROUTINE VISIT 2 l - 1ST VISIT - Dr. GADHIKAR HARSHAL ROUTINE VISIT 2 l - SUBSEaUENT - Dr. GADHIKAR HARSHAL</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1250</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19">
@@ -684,14 +694,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I.V.INFUSION</t>
+          <t>PROCEDURES:. BSL ON GLUCOMETER</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20">
@@ -700,14 +710,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INTRACATH INSERTION</t>
+          <t>ECG CHARGES ER1</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21">
@@ -716,14 +726,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
+          <t>ER CHARGES rPD</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="22">
@@ -732,14 +742,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
+          <t>I.V.INFUSION</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23">
@@ -748,14 +758,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
+          <t>INTRACATH INSERTION</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>90540.95</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="24">
@@ -764,15 +774,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bill :11842627/52655</t>
+          <t>OTHER CHARGES;- BIOMEDICAL WASTE DISPOSAL ERYOPD</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" t="n">
-        <v>1535.73</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -780,14 +788,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bill:11842627152785</t>
+          <t>BIOMEDICAL WASTE DISPOSAL WARDS</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>66.56</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="26">
@@ -796,14 +804,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bill :12072627155926</t>
+          <t>DRUGS AwD CONSUMABLES :- PHARMACY DRUGS</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>32.24</v>
+        <v>90540.95</v>
       </c>
     </row>
     <row r="27">
@@ -812,15 +820,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bill :10752627/59582</t>
+          <t>Bill :11842627/52655</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="n">
-        <v>84.41</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -828,15 +834,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bill:11842627153272</t>
+          <t>Bill:11842627152785</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" t="n">
-        <v>1722</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -844,15 +848,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bill :11842627153306</t>
+          <t>Bill :12072627155926</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" t="n">
-        <v>3608.2</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -860,15 +862,13 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
+          <t>Bill :10752627/59582</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="n">
-        <v>66.77</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -876,94 +876,86 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bill :11842627/53513</t>
+          <t>Bill:11842627153272</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="n">
-        <v>286.39</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bill:11842627153881</t>
+          <t>Bill :11842627153306</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="n">
-        <v>400</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bill:11842627154031</t>
+          <t>Bill :1 1842627/53353 Bill :11842627/53370</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" t="n">
-        <v>1148</v>
-      </c>
+      <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bill:11842627154078</t>
+          <t>Bill :11842627/53513</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="n">
-        <v>44.92</v>
-      </c>
+      <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bill:11842627154172</t>
+          <t>BED CHARGES</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1322</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bill:11842627154587</t>
+          <t>PHARMACY BILL</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>71.75</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="37">
@@ -972,14 +964,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bill :11842627/54609</t>
+          <t>Bill:11842627153881</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1722</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38">
@@ -988,14 +980,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bill:1082262717990</t>
+          <t>Bill:11842627154031</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1992.97</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="39">
@@ -1004,78 +996,78 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PHARMACY SALES RETURN</t>
+          <t>Bill:11842627154078</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-3585.94</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AL-01-4433 REVELOL AM 5O/5TAB</t>
+          <t>Bill:11842627154172</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.41</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Single ltem Pharmacy Retail</t>
+          <t>Bill:11842627154587</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>84.41</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SR.O2-01'16 EXTENSION TUBE lOCM WTH 5LO8S 3WAY</t>
+          <t>Bill :11842627/54609</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>280</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SR-02-2020 VENFLON SAFETY 2OG-393244</t>
+          <t>PHARMACY BILL Department : Bill:1082262717990</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>460.01</v>
+        <v>1992.97</v>
       </c>
     </row>
     <row r="44">
@@ -1084,14 +1076,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SR-03-0,149 S 95 A 6 F - E 62 P 2 ICO ASPIRATOR SYR 1.sIuL</t>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>45</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="45">
@@ -1100,14 +1092,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>sR-06-2151 GLOVES EXAM. MEXISAFEM</t>
+          <t>EXTENSION TUBE lOCM WTH 5LO8S</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46">
@@ -1116,14 +1108,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A1.03.0463 NS FLEXIDRIP IV 1OOML OTSUKA</t>
+          <t>VENFLON SAFETY 2OG-393244</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>44.92</v>
+        <v>460.01</v>
       </c>
     </row>
     <row r="47">
@@ -1132,14 +1124,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>41.03.0415 HOSPIMOL UB IV lOOOMG/1OOML</t>
+          <t>ASPIRATOR SYR 1.sIuL zKo1 o2t022028</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48">
@@ -1148,14 +1140,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AL.O3.OO54 PANTOCIDIV4OMG</t>
+          <t>GLOVES EXAM. MEXISAFEM 003</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>53.89</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1164,14 +1156,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sR-03-0075 5CCSYR OMNIVAN24X</t>
+          <t>NS FLEXIDRIP IV 1OOML OTSUKA</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="50">
@@ -1180,14 +1172,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SR.03.0148 I V SET ROfuISON TRANSFLOW.</t>
+          <t>HOSPIMOL UB IV lOOOMG/1OOML</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -1196,14 +1188,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SR-01-0673 VELFIX-EDGE 7X9CM</t>
+          <t>PANTOCIDIV4OMG NPC00048</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>213</v>
+        <v>53.89</v>
       </c>
     </row>
     <row r="52">
@@ -1212,14 +1204,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>sR-06-2953 0-SYTE BD-385103</t>
+          <t>5CCSYR OMNIVAN24X 1 25L13M4202</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>412</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -1228,14 +1220,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB</t>
+          <t>I V SET ROfuISON TRANSFLOW.</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54">
@@ -1244,25 +1236,30 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PROBE COVER FOR THERMOSCAN</t>
+          <t>VELFIX-EDGE 7X9CM</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0.62</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>4</v>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0-SYTE BD-385103</t>
+        </is>
+      </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>6.5</v>
+        <v>412</v>
       </c>
     </row>
     <row r="56">
@@ -1271,7 +1268,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PROBE COVER FOR THERMOSCAN</t>
+          <t>REVELOL AM 5O/5TAB JKN0'125006AS PROBE COVER FOR THERMOSCAN</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1287,14 +1284,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PAUSE INJ SOOI/lG/sML</t>
+          <t>PAUSE INJ SOOI/lG/sML EM260'192</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>147.38</v>
+        <v>294.76</v>
       </c>
     </row>
     <row r="58">
@@ -1303,7 +1300,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ONDEM INJ 4I'G/2ML</t>
+          <t>ONDEM INJ 4I'G/2ML SGOND26O79</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1355,10 +1352,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D61" t="n">
-        <v>55.5</v>
+        <v>2719.5</v>
       </c>
     </row>
     <row r="62">
@@ -1371,10 +1368,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>388.5</v>
+        <v>999</v>
       </c>
     </row>
     <row r="63">
@@ -1383,14 +1380,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>lOCC SYR OIVNIVAN 21 X 1.5</t>
+          <t>REVELOL AM 50/5TAB JKN0'125006AS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>92.51000000000001</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="64">
@@ -1399,14 +1396,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5CC SYR OMNIVAN 24 X 1</t>
+          <t>2CC SYR OMNIVAN 24 X 1</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>11</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="65">
@@ -1415,14 +1412,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ECOFLAC PLUS NS O.9GM/'IOOML</t>
+          <t>THALIX CAPS sOMG THA25O914</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>180</v>
+        <v>133.12</v>
       </c>
     </row>
     <row r="66">
@@ -1431,14 +1428,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ALCOHOL SWAB ROMSON</t>
+          <t>OCTRIDE INJ 100MCG/ML GTH0115A O1|12DO2A</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>19.25</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="67">
@@ -1447,14 +1444,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>REVELOL AM 5O/5TAB</t>
+          <t>IMLSYRTUBERCUIlN 6064263</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="D67" t="n">
-        <v>0.41</v>
+        <v>5184</v>
       </c>
     </row>
     <row r="68">
@@ -1463,14 +1460,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2CC SYR OMNIVAN 24 X 1</t>
+          <t>IRNY INJ 1000MG/20ML G250545</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>28.5</v>
+        <v>3608.2</v>
       </c>
     </row>
     <row r="69">
@@ -1479,14 +1476,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>THALIX CAPS sOMG</t>
+          <t>STERIPORT TOTAL NS IV 60650233</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>66.56</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="70">
@@ -1495,14 +1492,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OCTRIDE INJ 100MCG/|ML</t>
+          <t>STERIPORTTOTAL NS IV 60660233</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1650</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="71">
@@ -1511,62 +1508,62 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IMLSYRTUBERCUIlN</t>
+          <t>lML SYR TUBERCULIN 6064263</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
-        <v>72</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IRNY INJ 1000MG/20M1</t>
+          <t>THALIX CAPS SOMG TH4250914</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>3608.2</v>
+        <v>166.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>STERIPORTTOTAL NS IV 2 25GM/25OML AMANTA</t>
+          <t>TEGADERM 1633 lN7X8.5 R03260914</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>6.77</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>lML SYR TUBERCULIN</t>
+          <t>VASOFIX SAFETY 22G 25M10G8A0'1</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75">
@@ -1575,14 +1572,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>THALIX CAPS SOMG</t>
+          <t>IMLSYRTUBERCUL|N 6064263</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75" t="n">
-        <v>166.39</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76">
@@ -1591,14 +1588,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TEGADERM 1633 lN7X8.5</t>
+          <t>OCTRIDE INJ 100MCG/1ML GTH0115A</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>220</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="77">
@@ -1607,14 +1604,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VASOFIX SAFETY 22G</t>
+          <t>NS FLEXTDRTP lV I00MLOTSUKq</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>180</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="78">
@@ -1623,14 +1620,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IMLSYRTUBERCUL|N</t>
+          <t>OCTRIDEINJ'|ooMCG/|ML GTH0115A</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>48</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="79">
@@ -1639,14 +1636,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>OCTRIDE INJ 100MCG/1ML</t>
+          <t>POLYFLUSH SYRINGE 10ML</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>1100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80">
@@ -1655,14 +1652,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>OCTRIDEINJ'|ooMCG/|ML</t>
+          <t>MBLET TAB 2OMG U802884</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D80" t="n">
-        <v>550</v>
+        <v>358.75</v>
       </c>
     </row>
     <row r="81">
@@ -1671,14 +1668,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>POLYFLUSH SYRINGE 10ML</t>
+          <t>TMLSYRTUBERCULTN 6064263</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D81" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82">
@@ -1687,14 +1684,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MBLET TAB 2OMG</t>
+          <t>OCTRIDEINJ Io0MCG/1ML GTH0115A</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D82" t="n">
-        <v>71.75</v>
+        <v>4950</v>
       </c>
     </row>
     <row r="83">
@@ -1703,46 +1700,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>'TMLSYRTUBERCULTN</t>
+          <t>REVELOLAM 5O/5TAB JKN014008AS</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>72</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OCTRIDEINJ Io0MCG/1ML</t>
+          <t>Inj Octreotide lOOmcg 1-0-l for 15 days then stop</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>5</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>REVELOLAM 5O/5TAB</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>2</v>
-      </c>
-      <c r="D85" t="n">
-        <v>32.24</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
